--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136408393</v>
+        <v>136408138</v>
       </c>
       <c r="B8" t="n">
         <v>57990</v>
@@ -1445,20 +1445,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496760</v>
+        <v>496723</v>
       </c>
       <c r="R8" t="n">
-        <v>6613946</v>
+        <v>6613930</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1501,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,24 +1546,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carly Bishop, Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408393</t>
+          <t>https://artportalen.se/Sighting/136408138</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136409613</v>
+        <v>136408393</v>
       </c>
       <c r="B9" t="n">
         <v>57990</v>
@@ -1595,13 +1599,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496539</v>
+        <v>496760</v>
       </c>
       <c r="R9" t="n">
-        <v>6613892</v>
+        <v>6613946</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1630,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1644,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,9 +1676,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1686,13 +1700,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136409613</t>
+          <t>https://artportalen.se/Sighting/136408393</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136412164</v>
+        <v>136409613</v>
       </c>
       <c r="B10" t="n">
         <v>57990</v>
@@ -1721,24 +1735,20 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496453</v>
+        <v>496539</v>
       </c>
       <c r="R10" t="n">
-        <v>6613952</v>
+        <v>6613892</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1767,7 +1777,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1777,7 +1787,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,6 +1798,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1797,39 +1827,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Carly Bishop, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136412164</t>
+          <t>https://artportalen.se/Sighting/136409613</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136412874</v>
+        <v>136412164</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>57990</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1838,20 +1868,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496445</v>
+        <v>496453</v>
       </c>
       <c r="R11" t="n">
-        <v>6613950</v>
+        <v>6613952</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1880,7 +1914,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1890,12 +1924,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska spår på tall (det rinner kåda).</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1906,26 +1935,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1935,19 +1944,19 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carly Bishop, Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136412874</t>
+          <t>https://artportalen.se/Sighting/136412164</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136412943</v>
+        <v>136412874</v>
       </c>
       <c r="B12" t="n">
         <v>57993</v>
@@ -1979,17 +1988,17 @@
       <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vesenberget, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496678</v>
+        <v>496445</v>
       </c>
       <c r="R12" t="n">
-        <v>6613923</v>
+        <v>6613950</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2018,7 +2027,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2028,12 +2037,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>relativt gamla spår</t>
+          <t>Färska spår på tall (det rinner kåda).</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,17 +2061,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2079,59 +2088,55 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136412943</t>
+          <t>https://artportalen.se/Sighting/136412874</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136407329</v>
+        <v>136412943</v>
       </c>
       <c r="B13" t="n">
-        <v>57180</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496661</v>
+        <v>496678</v>
       </c>
       <c r="R13" t="n">
-        <v>6613872</v>
+        <v>6613923</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2160,7 +2165,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2170,7 +2175,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>relativt gamla spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2181,28 +2191,48 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136407329</t>
+          <t>https://artportalen.se/Sighting/136412943</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136407928</v>
+        <v>136407329</v>
       </c>
       <c r="B14" t="n">
         <v>57180</v>
@@ -2238,14 +2268,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Furumossen, Furumossen, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496802</v>
+        <v>496661</v>
       </c>
       <c r="R14" t="n">
-        <v>6613874</v>
+        <v>6613872</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2277,7 +2307,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2287,7 +2317,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2313,13 +2343,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136407928</t>
+          <t>https://artportalen.se/Sighting/136407329</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136407998</v>
+        <v>136407928</v>
       </c>
       <c r="B15" t="n">
         <v>57180</v>
@@ -2359,10 +2389,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496788</v>
+        <v>496802</v>
       </c>
       <c r="R15" t="n">
-        <v>6613880</v>
+        <v>6613874</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2394,7 +2424,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2404,7 +2434,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2430,13 +2460,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136407998</t>
+          <t>https://artportalen.se/Sighting/136407928</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136408837</v>
+        <v>136407998</v>
       </c>
       <c r="B16" t="n">
         <v>57180</v>
@@ -2467,22 +2497,22 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496621</v>
+        <v>496788</v>
       </c>
       <c r="R16" t="n">
-        <v>6613926</v>
+        <v>6613880</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2511,7 +2541,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2521,7 +2551,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2547,13 +2577,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408837</t>
+          <t>https://artportalen.se/Sighting/136407998</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136409421</v>
+        <v>136408837</v>
       </c>
       <c r="B17" t="n">
         <v>57180</v>
@@ -2593,13 +2623,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496569</v>
+        <v>496621</v>
       </c>
       <c r="R17" t="n">
-        <v>6613922</v>
+        <v>6613926</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2628,7 +2658,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2638,12 +2668,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 stycken spillning</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,33 +2679,28 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136409421</t>
+          <t>https://artportalen.se/Sighting/136408837</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136409568</v>
+        <v>136409421</v>
       </c>
       <c r="B18" t="n">
         <v>57180</v>
@@ -2723,10 +2743,10 @@
         <v>496569</v>
       </c>
       <c r="R18" t="n">
-        <v>6613923</v>
+        <v>6613922</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2755,7 +2775,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2765,7 +2785,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 stycken spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2796,13 +2821,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136409568</t>
+          <t>https://artportalen.se/Sighting/136409421</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136414831</v>
+        <v>136409568</v>
       </c>
       <c r="B19" t="n">
         <v>57180</v>
@@ -2842,13 +2867,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496617</v>
+        <v>496569</v>
       </c>
       <c r="R19" t="n">
-        <v>6613879</v>
+        <v>6613923</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2877,7 +2902,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2887,7 +2912,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2898,31 +2923,36 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136414831</t>
+          <t>https://artportalen.se/Sighting/136409568</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136406946</v>
+        <v>136414831</v>
       </c>
       <c r="B20" t="n">
-        <v>4777</v>
+        <v>57180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,37 +2960,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496593</v>
+        <v>496617</v>
       </c>
       <c r="R20" t="n">
-        <v>6613873</v>
+        <v>6613879</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2989,7 +3024,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2999,7 +3034,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3025,13 +3060,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136406946</t>
+          <t>https://artportalen.se/Sighting/136414831</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136408466</v>
+        <v>136406946</v>
       </c>
       <c r="B21" t="n">
         <v>4777</v>
@@ -3062,17 +3097,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Furumossen, Furumossen, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496730</v>
+        <v>496593</v>
       </c>
       <c r="R21" t="n">
-        <v>6613975</v>
+        <v>6613873</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3101,7 +3136,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3111,7 +3146,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3137,16 +3172,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408466</t>
+          <t>https://artportalen.se/Sighting/136406946</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136411492</v>
+        <v>136408466</v>
       </c>
       <c r="B22" t="n">
-        <v>5182</v>
+        <v>4777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3154,37 +3189,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496464</v>
+        <v>496730</v>
       </c>
       <c r="R22" t="n">
-        <v>6613962</v>
+        <v>6613975</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3213,7 +3248,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3223,7 +3258,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3234,103 +3269,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136411492</t>
+          <t>https://artportalen.se/Sighting/136408466</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136408636</v>
+        <v>136411492</v>
       </c>
       <c r="B23" t="n">
-        <v>99327</v>
+        <v>5182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496706</v>
+        <v>496464</v>
       </c>
       <c r="R23" t="n">
-        <v>6613957</v>
+        <v>6613962</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3359,7 +3360,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3369,7 +3370,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3384,6 +3385,21 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3400,16 +3416,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408636</t>
+          <t>https://artportalen.se/Sighting/136411492</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136408641</v>
+        <v>136408636</v>
       </c>
       <c r="B24" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3436,7 +3452,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3451,17 +3467,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Furumossen, Furumossen, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496698</v>
+        <v>496706</v>
       </c>
       <c r="R24" t="n">
-        <v>6613984</v>
+        <v>6613957</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3490,7 +3506,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3500,7 +3516,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3511,31 +3527,36 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408641</t>
+          <t>https://artportalen.se/Sighting/136408636</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136408673</v>
+        <v>136408641</v>
       </c>
       <c r="B25" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3562,7 +3583,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3581,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496707</v>
+        <v>496698</v>
       </c>
       <c r="R25" t="n">
-        <v>6613977</v>
+        <v>6613984</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3616,7 +3637,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3626,7 +3647,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3652,16 +3673,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408673</t>
+          <t>https://artportalen.se/Sighting/136408641</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136408778</v>
+        <v>136408673</v>
       </c>
       <c r="B26" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3688,7 +3709,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3698,17 +3724,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496716</v>
+        <v>496707</v>
       </c>
       <c r="R26" t="n">
-        <v>6613945</v>
+        <v>6613977</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3737,7 +3763,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3747,7 +3773,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3762,16 +3788,137 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136408673</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136408778</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99328</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vesenberget, Vesenberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496716</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6613945</v>
+      </c>
+      <c r="S27" t="n">
+        <v>11</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Järnboås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Carly Bishop</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Carly Bishop</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136408778</t>
         </is>
@@ -3804,6 +3951,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>136405803</v>
       </c>
       <c r="B4" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136407033</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136407810</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>136408042</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>136408138</v>
       </c>
       <c r="B8" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>136408393</v>
       </c>
       <c r="B9" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>136409613</v>
       </c>
       <c r="B10" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>136412164</v>
       </c>
       <c r="B11" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136412874</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>136412943</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>136407329</v>
       </c>
       <c r="B14" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>136407928</v>
       </c>
       <c r="B15" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136407998</v>
       </c>
       <c r="B16" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>136408837</v>
       </c>
       <c r="B17" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136409421</v>
       </c>
       <c r="B18" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>136409568</v>
       </c>
       <c r="B19" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136414831</v>
       </c>
       <c r="B20" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136408636</v>
       </c>
       <c r="B24" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>136408641</v>
       </c>
       <c r="B25" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>136408673</v>
       </c>
       <c r="B26" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>136408778</v>
       </c>
       <c r="B27" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136407810</v>
+        <v>136407363</v>
       </c>
       <c r="B6" t="n">
         <v>58003</v>
@@ -1216,24 +1216,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Furumossen, Furumossen, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496766</v>
+        <v>496678</v>
       </c>
       <c r="R6" t="n">
-        <v>6613890</v>
+        <v>6613923</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1261,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1271,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla spår på 2 gamla träd som står nära varandra.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,28 +1287,53 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136407810</t>
+          <t>https://artportalen.se/Sighting/136407363</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136408042</v>
+        <v>136407810</v>
       </c>
       <c r="B7" t="n">
         <v>58003</v>
@@ -1333,16 +1362,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496788</v>
+        <v>496766</v>
       </c>
       <c r="R7" t="n">
-        <v>6613880</v>
+        <v>6613890</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1374,7 +1408,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1384,7 +1418,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,13 +1444,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408042</t>
+          <t>https://artportalen.se/Sighting/136407810</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136408138</v>
+        <v>136408042</v>
       </c>
       <c r="B8" t="n">
         <v>58003</v>
@@ -1445,21 +1479,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496723</v>
+        <v>496788</v>
       </c>
       <c r="R8" t="n">
-        <v>6613930</v>
+        <v>6613880</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1491,7 +1520,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1501,12 +1530,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,53 +1541,28 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408138</t>
+          <t>https://artportalen.se/Sighting/136408042</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136408393</v>
+        <v>136408138</v>
       </c>
       <c r="B9" t="n">
         <v>58003</v>
@@ -1592,20 +1591,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496760</v>
+        <v>496723</v>
       </c>
       <c r="R9" t="n">
-        <v>6613946</v>
+        <v>6613930</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1634,7 +1637,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,12 +1647,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1689,24 +1692,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carly Bishop, Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408393</t>
+          <t>https://artportalen.se/Sighting/136408138</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136409613</v>
+        <v>136408393</v>
       </c>
       <c r="B10" t="n">
         <v>58003</v>
@@ -1742,13 +1745,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496539</v>
+        <v>496760</v>
       </c>
       <c r="R10" t="n">
-        <v>6613892</v>
+        <v>6613946</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1777,7 +1780,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1787,7 +1790,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,9 +1822,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1833,13 +1846,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136409613</t>
+          <t>https://artportalen.se/Sighting/136408393</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136412164</v>
+        <v>136409613</v>
       </c>
       <c r="B11" t="n">
         <v>58003</v>
@@ -1868,24 +1881,20 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496453</v>
+        <v>496539</v>
       </c>
       <c r="R11" t="n">
-        <v>6613952</v>
+        <v>6613892</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1914,7 +1923,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1924,7 +1933,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,6 +1944,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1944,39 +1973,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Carly Bishop, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136412164</t>
+          <t>https://artportalen.se/Sighting/136409613</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136412874</v>
+        <v>136412164</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>58003</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1985,20 +2014,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496445</v>
+        <v>496453</v>
       </c>
       <c r="R12" t="n">
-        <v>6613950</v>
+        <v>6613952</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2027,7 +2060,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2037,12 +2070,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska spår på tall (det rinner kåda).</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,26 +2081,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2082,19 +2090,19 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carly Bishop, Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136412874</t>
+          <t>https://artportalen.se/Sighting/136412164</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136412943</v>
+        <v>136412874</v>
       </c>
       <c r="B13" t="n">
         <v>58006</v>
@@ -2126,17 +2134,17 @@
       <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vesenberget, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496678</v>
+        <v>496445</v>
       </c>
       <c r="R13" t="n">
-        <v>6613923</v>
+        <v>6613950</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2165,7 +2173,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2175,12 +2183,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>relativt gamla spår</t>
+          <t>Färska spår på tall (det rinner kåda).</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2199,17 +2207,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2226,59 +2234,55 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136412943</t>
+          <t>https://artportalen.se/Sighting/136412874</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136407329</v>
+        <v>136412943</v>
       </c>
       <c r="B14" t="n">
-        <v>57193</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496661</v>
+        <v>496678</v>
       </c>
       <c r="R14" t="n">
-        <v>6613872</v>
+        <v>6613923</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2317,7 +2321,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>relativt gamla spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,28 +2337,48 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136407329</t>
+          <t>https://artportalen.se/Sighting/136412943</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136407928</v>
+        <v>136407329</v>
       </c>
       <c r="B15" t="n">
         <v>57193</v>
@@ -2385,14 +2414,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Furumossen, Furumossen, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496802</v>
+        <v>496661</v>
       </c>
       <c r="R15" t="n">
-        <v>6613874</v>
+        <v>6613872</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2424,7 +2453,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2434,7 +2463,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2460,13 +2489,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136407928</t>
+          <t>https://artportalen.se/Sighting/136407329</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136407998</v>
+        <v>136407928</v>
       </c>
       <c r="B16" t="n">
         <v>57193</v>
@@ -2506,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496788</v>
+        <v>496802</v>
       </c>
       <c r="R16" t="n">
-        <v>6613880</v>
+        <v>6613874</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2541,7 +2570,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2551,7 +2580,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2577,13 +2606,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136407998</t>
+          <t>https://artportalen.se/Sighting/136407928</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136408837</v>
+        <v>136407998</v>
       </c>
       <c r="B17" t="n">
         <v>57193</v>
@@ -2614,22 +2643,22 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496621</v>
+        <v>496788</v>
       </c>
       <c r="R17" t="n">
-        <v>6613926</v>
+        <v>6613880</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2658,7 +2687,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2668,7 +2697,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2694,13 +2723,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408837</t>
+          <t>https://artportalen.se/Sighting/136407998</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136409421</v>
+        <v>136408837</v>
       </c>
       <c r="B18" t="n">
         <v>57193</v>
@@ -2740,13 +2769,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496569</v>
+        <v>496621</v>
       </c>
       <c r="R18" t="n">
-        <v>6613922</v>
+        <v>6613926</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2775,7 +2804,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2785,12 +2814,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 stycken spillning</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2801,33 +2825,28 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136409421</t>
+          <t>https://artportalen.se/Sighting/136408837</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136409568</v>
+        <v>136409421</v>
       </c>
       <c r="B19" t="n">
         <v>57193</v>
@@ -2870,10 +2889,10 @@
         <v>496569</v>
       </c>
       <c r="R19" t="n">
-        <v>6613923</v>
+        <v>6613922</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2902,7 +2921,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2912,7 +2931,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 stycken spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2943,13 +2967,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136409568</t>
+          <t>https://artportalen.se/Sighting/136409421</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136414831</v>
+        <v>136409568</v>
       </c>
       <c r="B20" t="n">
         <v>57193</v>
@@ -2989,13 +3013,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496617</v>
+        <v>496569</v>
       </c>
       <c r="R20" t="n">
-        <v>6613879</v>
+        <v>6613923</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3024,7 +3048,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3034,7 +3058,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3045,31 +3069,36 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136414831</t>
+          <t>https://artportalen.se/Sighting/136409568</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136406946</v>
+        <v>136411323</v>
       </c>
       <c r="B21" t="n">
-        <v>4777</v>
+        <v>57193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3077,37 +3106,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496593</v>
+        <v>496678</v>
       </c>
       <c r="R21" t="n">
-        <v>6613873</v>
+        <v>6613923</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3136,7 +3165,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3146,7 +3175,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3157,31 +3186,36 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136406946</t>
+          <t>https://artportalen.se/Sighting/136411323</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136408466</v>
+        <v>136414831</v>
       </c>
       <c r="B22" t="n">
-        <v>4777</v>
+        <v>57193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3189,37 +3223,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Furumossen, Furumossen, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496730</v>
+        <v>496617</v>
       </c>
       <c r="R22" t="n">
-        <v>6613975</v>
+        <v>6613879</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3248,7 +3287,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,7 +3297,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3284,16 +3323,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408466</t>
+          <t>https://artportalen.se/Sighting/136414831</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136411492</v>
+        <v>136406946</v>
       </c>
       <c r="B23" t="n">
-        <v>5182</v>
+        <v>4777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3301,21 +3340,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3325,13 +3364,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496464</v>
+        <v>496593</v>
       </c>
       <c r="R23" t="n">
-        <v>6613962</v>
+        <v>6613873</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3360,7 +3399,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3370,7 +3409,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3381,103 +3420,69 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136411492</t>
+          <t>https://artportalen.se/Sighting/136406946</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136408636</v>
+        <v>136408466</v>
       </c>
       <c r="B24" t="n">
-        <v>99341</v>
+        <v>4777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496706</v>
+        <v>496730</v>
       </c>
       <c r="R24" t="n">
-        <v>6613957</v>
+        <v>6613975</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3506,7 +3511,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3516,7 +3521,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3527,88 +3532,69 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408636</t>
+          <t>https://artportalen.se/Sighting/136408466</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136408641</v>
+        <v>136411492</v>
       </c>
       <c r="B25" t="n">
-        <v>99341</v>
+        <v>5182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Furumossen, Furumossen, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496698</v>
+        <v>496464</v>
       </c>
       <c r="R25" t="n">
-        <v>6613984</v>
+        <v>6613962</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3637,7 +3623,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3647,7 +3633,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3658,31 +3644,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408641</t>
+          <t>https://artportalen.se/Sighting/136411492</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136408673</v>
+        <v>136408636</v>
       </c>
       <c r="B26" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3715,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3724,17 +3730,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Furumossen, Furumossen, Vstm</t>
+          <t>Vesenberget, Vesenberget, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496707</v>
+        <v>496706</v>
       </c>
       <c r="R26" t="n">
-        <v>6613977</v>
+        <v>6613957</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3763,7 +3769,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3773,7 +3779,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3784,31 +3790,36 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Carly Bishop</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136408673</t>
+          <t>https://artportalen.se/Sighting/136408636</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136408778</v>
+        <v>136408641</v>
       </c>
       <c r="B27" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3835,7 +3846,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3845,17 +3861,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vesenberget, Vesenberget, Vstm</t>
+          <t>Furumossen, Furumossen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496716</v>
+        <v>496698</v>
       </c>
       <c r="R27" t="n">
-        <v>6613945</v>
+        <v>6613984</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3884,7 +3900,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3894,7 +3910,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3909,16 +3925,263 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carly Bishop</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136408641</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136408673</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Furumossen, Furumossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>496707</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6613977</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Järnboås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136408673</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136408778</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vesenberget, Vesenberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>496716</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6613945</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Järnboås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Carly Bishop</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Carly Bishop</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136408778</t>
         </is>
@@ -3952,6 +4215,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
